--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_metropolitana.xlsx
@@ -404,7 +404,7 @@
         <v>17.02924978221389</v>
       </c>
       <c r="D2">
-        <v>2.685682335493184</v>
+        <v>4.949212241676654</v>
       </c>
       <c r="E2">
         <v>14.72314750260369</v>
@@ -429,7 +429,7 @@
         <v>27.01404286770141</v>
       </c>
       <c r="D3">
-        <v>1.705426356589147</v>
+        <v>3.162323244127615</v>
       </c>
       <c r="E3">
         <v>19.93384117222261</v>
@@ -454,7 +454,7 @@
         <v>26.67648192940022</v>
       </c>
       <c r="D4">
-        <v>1.660155189136761</v>
+        <v>2.979839832869081</v>
       </c>
       <c r="E4">
         <v>20.94347740481729</v>
@@ -479,7 +479,7 @@
         <v>25.56824105932645</v>
       </c>
       <c r="D5">
-        <v>1.564472718375336</v>
+        <v>2.607489974852172</v>
       </c>
       <c r="E5">
         <v>23.39630442387813</v>
@@ -504,7 +504,7 @@
         <v>27.05992799149928</v>
       </c>
       <c r="D6">
-        <v>1.551797006323541</v>
+        <v>2.675120739616393</v>
       </c>
       <c r="E6">
         <v>22.7324056763573</v>
@@ -529,7 +529,7 @@
         <v>25.26076538163366</v>
       </c>
       <c r="D7">
-        <v>1.91600837215583</v>
+        <v>3.713182859012103</v>
       </c>
       <c r="E7">
         <v>17.69547801523536</v>
@@ -554,7 +554,7 @@
         <v>26.38446344382128</v>
       </c>
       <c r="D8">
-        <v>1.913246165728788</v>
+        <v>3.863580659536542</v>
       </c>
       <c r="E8">
         <v>16.99822935110926</v>
@@ -579,7 +579,7 @@
         <v>24.62273703968979</v>
       </c>
       <c r="D9">
-        <v>1.965628565186785</v>
+        <v>3.809295324113275</v>
       </c>
       <c r="E9">
         <v>17.39963167587477</v>
@@ -604,7 +604,7 @@
         <v>23.96306318702319</v>
       </c>
       <c r="D10">
-        <v>1.744612183932572</v>
+        <v>2.997937482812357</v>
       </c>
       <c r="E10">
         <v>21.20290376186821</v>
@@ -629,7 +629,7 @@
         <v>23.54612299465241</v>
       </c>
       <c r="D11">
-        <v>1.650140000565659</v>
+        <v>2.698706014315945</v>
       </c>
       <c r="E11">
         <v>23.07259260840333</v>
@@ -654,7 +654,7 @@
         <v>25.47774107704035</v>
       </c>
       <c r="D12">
-        <v>1.560171082829126</v>
+        <v>2.589479880878177</v>
       </c>
       <c r="E12">
         <v>23.53372613255751</v>
@@ -679,7 +679,7 @@
         <v>30.64308221140075</v>
       </c>
       <c r="D13">
-        <v>1.652153336488405</v>
+        <v>3.346273664030673</v>
       </c>
       <c r="E13">
         <v>18.6161670235546</v>
@@ -704,7 +704,7 @@
         <v>24.20610072457286</v>
       </c>
       <c r="D14">
-        <v>1.516742646260719</v>
+        <v>2.396664093988509</v>
       </c>
       <c r="E14">
         <v>25.14582681919631</v>
@@ -729,7 +729,7 @@
         <v>20.25088847520731</v>
       </c>
       <c r="D15">
-        <v>1.651712089447938</v>
+        <v>2.481860660471465</v>
       </c>
       <c r="E15">
         <v>25.09750698360829</v>
@@ -754,7 +754,7 @@
         <v>26.18333762939046</v>
       </c>
       <c r="D16">
-        <v>1.882351439005082</v>
+        <v>3.711717609144468</v>
       </c>
       <c r="E16">
         <v>17.59457783290511</v>
@@ -779,7 +779,7 @@
         <v>26.62507940127368</v>
       </c>
       <c r="D17">
-        <v>1.581174349729591</v>
+        <v>2.730818840902015</v>
       </c>
       <c r="E17">
         <v>22.43207918026081</v>
@@ -804,7 +804,7 @@
         <v>24.56194073015549</v>
       </c>
       <c r="D18">
-        <v>1.616800066012047</v>
+        <v>2.681782928053287</v>
       </c>
       <c r="E18">
         <v>23.03892199833927</v>
@@ -829,7 +829,7 @@
         <v>21.69824263816307</v>
       </c>
       <c r="D19">
-        <v>1.708474504038015</v>
+        <v>2.714919409454152</v>
       </c>
       <c r="E19">
         <v>23.23415102355514</v>
@@ -854,7 +854,7 @@
         <v>24.16428885881528</v>
       </c>
       <c r="D20">
-        <v>1.66521859540708</v>
+        <v>2.786455493766583</v>
       </c>
       <c r="E20">
         <v>22.42261739824942</v>
@@ -879,7 +879,7 @@
         <v>18.6142933687138</v>
       </c>
       <c r="D21">
-        <v>1.934644717032357</v>
+        <v>3.023451361567538</v>
       </c>
       <c r="E21">
         <v>21.80432789752992</v>
@@ -904,7 +904,7 @@
         <v>25.9632231337296</v>
       </c>
       <c r="D22">
-        <v>1.424163984888764</v>
+        <v>2.259712869089026</v>
       </c>
       <c r="E22">
         <v>25.99828768770502</v>
@@ -929,7 +929,7 @@
         <v>24.37674747487853</v>
       </c>
       <c r="D23">
-        <v>1.801881940385739</v>
+        <v>3.213286640401893</v>
       </c>
       <c r="E23">
         <v>20.01368371429406</v>
@@ -954,7 +954,7 @@
         <v>14.62804403424886</v>
       </c>
       <c r="D24">
-        <v>2.091516948659806</v>
+        <v>3.013487475915221</v>
       </c>
       <c r="E24">
         <v>22.45020782005228</v>
@@ -979,7 +979,7 @@
         <v>27.24274500306299</v>
       </c>
       <c r="D25">
-        <v>1.716168308843305</v>
+        <v>3.22304107261749</v>
       </c>
       <c r="E25">
         <v>19.60366896502061</v>
@@ -1004,7 +1004,7 @@
         <v>26.84533811153951</v>
       </c>
       <c r="D26">
-        <v>2.050333076021385</v>
+        <v>4.560540540540541</v>
       </c>
       <c r="E26">
         <v>14.73875613333771</v>
@@ -1029,7 +1029,7 @@
         <v>24.24442531514216</v>
       </c>
       <c r="D27">
-        <v>1.785815065175732</v>
+        <v>3.149366806551046</v>
       </c>
       <c r="E27">
         <v>20.35452415148537</v>
@@ -1054,7 +1054,7 @@
         <v>24.73511451095546</v>
       </c>
       <c r="D28">
-        <v>1.743141250305648</v>
+        <v>3.06442183693939</v>
       </c>
       <c r="E28">
         <v>20.73651933110686</v>
@@ -1079,7 +1079,7 @@
         <v>28.7999741791109</v>
       </c>
       <c r="D29">
-        <v>1.695048782711772</v>
+        <v>3.311765125062353</v>
       </c>
       <c r="E29">
         <v>18.99135895197688</v>
@@ -1104,7 +1104,7 @@
         <v>24.45419637959408</v>
       </c>
       <c r="D30">
-        <v>1.594049016913583</v>
+        <v>2.612389452997052</v>
       </c>
       <c r="E30">
         <v>23.5226134525002</v>
@@ -1129,7 +1129,7 @@
         <v>23.01502586419246</v>
       </c>
       <c r="D31">
-        <v>1.97666916881378</v>
+        <v>3.626456247441099</v>
       </c>
       <c r="E31">
         <v>18.31137585790912</v>
@@ -1154,7 +1154,7 @@
         <v>25.27669025749134</v>
       </c>
       <c r="D32">
-        <v>1.616306662610283</v>
+        <v>2.732781235533152</v>
       </c>
       <c r="E32">
         <v>22.6063396823182</v>
@@ -1179,7 +1179,7 @@
         <v>23.40445407667588</v>
       </c>
       <c r="D33">
-        <v>1.538797688526004</v>
+        <v>2.404924514737599</v>
       </c>
       <c r="E33">
         <v>25.20298504082349</v>
@@ -1204,7 +1204,7 @@
         <v>26.90396574892965</v>
       </c>
       <c r="D34">
-        <v>1.726934644274689</v>
+        <v>3.22558740515377</v>
       </c>
       <c r="E34">
         <v>19.63325728843566</v>
@@ -1229,7 +1229,7 @@
         <v>21.82837325590774</v>
       </c>
       <c r="D35">
-        <v>1.907098361916481</v>
+        <v>3.267193675889328</v>
       </c>
       <c r="E35">
         <v>20.07883389328325</v>
@@ -1254,7 +1254,7 @@
         <v>23.99802890932983</v>
       </c>
       <c r="D36">
-        <v>1.629332262812793</v>
+        <v>2.675455943748627</v>
       </c>
       <c r="E36">
         <v>23.16148404498957</v>
@@ -1279,7 +1279,7 @@
         <v>33.30439233032956</v>
       </c>
       <c r="D37">
-        <v>1.891114606197826</v>
+        <v>5.108693622186945</v>
       </c>
       <c r="E37">
         <v>12.80391207398507</v>
@@ -1304,7 +1304,7 @@
         <v>34.56161123270305</v>
       </c>
       <c r="D38">
-        <v>1.902673796791444</v>
+        <v>5.556788728650229</v>
       </c>
       <c r="E38">
         <v>11.79620251179855</v>
@@ -1329,7 +1329,7 @@
         <v>32.99050632911392</v>
       </c>
       <c r="D39">
-        <v>1.919805589307412</v>
+        <v>5.236122618061309</v>
       </c>
       <c r="E39">
         <v>12.55722014148981</v>
@@ -1354,7 +1354,7 @@
         <v>29.25192145226762</v>
       </c>
       <c r="D40">
-        <v>1.740054857388717</v>
+        <v>3.543896160797415</v>
       </c>
       <c r="E40">
         <v>17.91936824061291</v>
@@ -1379,7 +1379,7 @@
         <v>30.98347513512116</v>
       </c>
       <c r="D41">
-        <v>1.778457434576645</v>
+        <v>3.961175988526941</v>
       </c>
       <c r="E41">
         <v>16.15904125008277</v>
@@ -1404,7 +1404,7 @@
         <v>20.04826754007929</v>
       </c>
       <c r="D42">
-        <v>2.001207416990082</v>
+        <v>3.342071150799366</v>
       </c>
       <c r="E42">
         <v>19.95172275065375</v>
@@ -1429,7 +1429,7 @@
         <v>29.38023963557019</v>
       </c>
       <c r="D43">
-        <v>1.678909990680935</v>
+        <v>3.313209461601877</v>
       </c>
       <c r="E43">
         <v>18.91561206741439</v>
@@ -1454,7 +1454,7 @@
         <v>29.71694394070803</v>
       </c>
       <c r="D44">
-        <v>1.589319919084871</v>
+        <v>3.011771490603162</v>
       </c>
       <c r="E44">
         <v>20.37997262205998</v>
@@ -1479,7 +1479,7 @@
         <v>33.62782992821646</v>
       </c>
       <c r="D45">
-        <v>1.520570948782536</v>
+        <v>3.111683848797251</v>
       </c>
       <c r="E45">
         <v>19.38707528314457</v>
@@ -1504,7 +1504,7 @@
         <v>29.19514212336221</v>
       </c>
       <c r="D46">
-        <v>1.52806970866037</v>
+        <v>2.758856731115648</v>
       </c>
       <c r="E46">
         <v>21.9091220038414</v>
@@ -1529,7 +1529,7 @@
         <v>29.41825476429288</v>
       </c>
       <c r="D47">
-        <v>1.494528556438315</v>
+        <v>2.667201712145532</v>
       </c>
       <c r="E47">
         <v>22.46259239228412</v>
@@ -1554,7 +1554,7 @@
         <v>32.56806475349522</v>
       </c>
       <c r="D48">
-        <v>1.36145061109998</v>
+        <v>2.446004319654428</v>
       </c>
       <c r="E48">
         <v>23.5703376887833</v>
@@ -1579,7 +1579,7 @@
         <v>27.57845749970168</v>
       </c>
       <c r="D49">
-        <v>1.683135837182834</v>
+        <v>3.141250702817517</v>
       </c>
       <c r="E49">
         <v>19.96980887269824</v>
@@ -1604,7 +1604,7 @@
         <v>29.16650136866744</v>
       </c>
       <c r="D50">
-        <v>1.656720341767992</v>
+        <v>3.205773877654839</v>
       </c>
       <c r="E50">
         <v>19.45227846222354</v>
@@ -1629,7 +1629,7 @@
         <v>27.32310476118672</v>
       </c>
       <c r="D51">
-        <v>1.725894599869876</v>
+        <v>3.26606747106624</v>
       </c>
       <c r="E51">
         <v>19.38563620306943</v>
@@ -1654,7 +1654,7 @@
         <v>29.97454352324964</v>
       </c>
       <c r="D52">
-        <v>1.852016416239867</v>
+        <v>4.163083257090577</v>
       </c>
       <c r="E52">
         <v>15.59831600979949</v>
@@ -1679,7 +1679,7 @@
         <v>27.08237308224139</v>
       </c>
       <c r="D53">
-        <v>1.736500585998914</v>
+        <v>3.278182504991636</v>
       </c>
       <c r="E53">
         <v>19.35736595251277</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_metropolitana.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>17.02924978221389</v>
+      </c>
+      <c r="C2">
         <v>20.20523572578145</v>
-      </c>
-      <c r="C2">
-        <v>17.02924978221389</v>
       </c>
       <c r="D2">
         <v>4.949212241676654</v>
       </c>
       <c r="E2">
-        <v>14.72314750260369</v>
+        <v>12.40887064149904</v>
       </c>
       <c r="F2">
         <v>72.86798185589726</v>
       </c>
       <c r="G2">
-        <v>12.40887064149904</v>
+        <v>14.72314750260369</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.01404286770141</v>
+      </c>
+      <c r="C3">
         <v>31.62232076866223</v>
-      </c>
-      <c r="C3">
-        <v>27.01404286770141</v>
       </c>
       <c r="D3">
         <v>3.162323244127615</v>
       </c>
       <c r="E3">
-        <v>19.93384117222261</v>
+        <v>17.02890954410977</v>
       </c>
       <c r="F3">
         <v>63.03724928366763</v>
       </c>
       <c r="G3">
-        <v>17.02890954410977</v>
+        <v>19.93384117222261</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>26.67648192940022</v>
+      </c>
+      <c r="C4">
         <v>33.55885067947325</v>
-      </c>
-      <c r="C4">
-        <v>26.67648192940022</v>
       </c>
       <c r="D4">
         <v>2.979839832869081</v>
       </c>
       <c r="E4">
-        <v>20.94347740481729</v>
+        <v>16.64831438551458</v>
       </c>
       <c r="F4">
         <v>62.40820820966813</v>
       </c>
       <c r="G4">
-        <v>16.64831438551458</v>
+        <v>20.94347740481729</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>25.56824105932645</v>
+      </c>
+      <c r="C5">
         <v>38.35105828380774</v>
-      </c>
-      <c r="C5">
-        <v>25.56824105932645</v>
       </c>
       <c r="D5">
         <v>2.607489974852172</v>
       </c>
       <c r="E5">
-        <v>23.39630442387813</v>
+        <v>15.59806634227014</v>
       </c>
       <c r="F5">
         <v>61.00562923385174</v>
       </c>
       <c r="G5">
-        <v>15.59806634227014</v>
+        <v>23.39630442387813</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.05992799149928</v>
+      </c>
+      <c r="C6">
         <v>37.38149030773833</v>
-      </c>
-      <c r="C6">
-        <v>27.05992799149928</v>
       </c>
       <c r="D6">
         <v>2.675120739616393</v>
       </c>
       <c r="E6">
-        <v>22.7324056763573</v>
+        <v>16.45566443744589</v>
       </c>
       <c r="F6">
-        <v>60.81192988619682</v>
+        <v>60.81192988619681</v>
       </c>
       <c r="G6">
-        <v>16.45566443744589</v>
+        <v>22.73240567635729</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.26076538163366</v>
+      </c>
+      <c r="C7">
         <v>26.93107336669251</v>
-      </c>
-      <c r="C7">
-        <v>25.26076538163366</v>
       </c>
       <c r="D7">
         <v>3.713182859012103</v>
       </c>
       <c r="E7">
-        <v>17.69547801523536</v>
+        <v>16.59797633656718</v>
       </c>
       <c r="F7">
         <v>65.70654564819745</v>
       </c>
       <c r="G7">
-        <v>16.59797633656718</v>
+        <v>17.69547801523536</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.38446344382128</v>
+      </c>
+      <c r="C8">
         <v>25.88272610620107</v>
-      </c>
-      <c r="C8">
-        <v>26.38446344382128</v>
       </c>
       <c r="D8">
         <v>3.863580659536542</v>
       </c>
       <c r="E8">
-        <v>16.99822935110926</v>
+        <v>17.32774048157862</v>
       </c>
       <c r="F8">
         <v>65.67403016731211</v>
       </c>
       <c r="G8">
-        <v>17.32774048157862</v>
+        <v>16.99822935110926</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>24.62273703968979</v>
+      </c>
+      <c r="C9">
         <v>26.25157450171652</v>
-      </c>
-      <c r="C9">
-        <v>24.62273703968979</v>
       </c>
       <c r="D9">
         <v>3.809295324113275</v>
       </c>
       <c r="E9">
-        <v>17.39963167587477</v>
+        <v>16.32003273992224</v>
       </c>
       <c r="F9">
         <v>66.28033558420299</v>
       </c>
       <c r="G9">
-        <v>16.32003273992224</v>
+        <v>17.39963167587477</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>23.96306318702319</v>
+      </c>
+      <c r="C10">
         <v>33.35626595728417</v>
-      </c>
-      <c r="C10">
-        <v>23.96306318702319</v>
       </c>
       <c r="D10">
         <v>2.997937482812357</v>
       </c>
       <c r="E10">
-        <v>21.20290376186821</v>
+        <v>15.23211630596398</v>
       </c>
       <c r="F10">
         <v>63.56497993216782</v>
       </c>
       <c r="G10">
-        <v>15.23211630596398</v>
+        <v>21.20290376186821</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>23.54612299465241</v>
+      </c>
+      <c r="C11">
         <v>37.05479569450157</v>
-      </c>
-      <c r="C11">
-        <v>23.54612299465241</v>
       </c>
       <c r="D11">
         <v>2.698706014315945</v>
       </c>
       <c r="E11">
-        <v>23.07259260840333</v>
+        <v>14.661262953437</v>
       </c>
       <c r="F11">
-        <v>62.26614443815969</v>
+        <v>62.26614443815968</v>
       </c>
       <c r="G11">
-        <v>14.661262953437</v>
+        <v>23.07259260840332</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.47774107704035</v>
+      </c>
+      <c r="C12">
         <v>38.61779376562939</v>
-      </c>
-      <c r="C12">
-        <v>25.47774107704035</v>
       </c>
       <c r="D12">
         <v>2.589479880878177</v>
       </c>
       <c r="E12">
-        <v>23.53372613255751</v>
+        <v>15.52616352508781</v>
       </c>
       <c r="F12">
         <v>60.94011034235468</v>
       </c>
       <c r="G12">
-        <v>15.52616352508781</v>
+        <v>23.53372613255751</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>30.64308221140075</v>
+      </c>
+      <c r="C13">
         <v>29.88398739616156</v>
-      </c>
-      <c r="C13">
-        <v>30.64308221140075</v>
       </c>
       <c r="D13">
         <v>3.346273664030673</v>
       </c>
       <c r="E13">
-        <v>18.6161670235546</v>
+        <v>19.08904354032834</v>
       </c>
       <c r="F13">
         <v>62.29478943611706</v>
       </c>
       <c r="G13">
-        <v>19.08904354032834</v>
+        <v>18.6161670235546</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>24.20610072457286</v>
+      </c>
+      <c r="C14">
         <v>41.72466231326595</v>
-      </c>
-      <c r="C14">
-        <v>24.20610072457286</v>
       </c>
       <c r="D14">
         <v>2.396664093988509</v>
       </c>
       <c r="E14">
-        <v>25.14582681919631</v>
+        <v>14.58807292958263</v>
       </c>
       <c r="F14">
         <v>60.26610025122107</v>
       </c>
       <c r="G14">
-        <v>14.58807292958263</v>
+        <v>25.14582681919631</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>20.25088847520731</v>
+      </c>
+      <c r="C15">
         <v>40.29235065154849</v>
-      </c>
-      <c r="C15">
-        <v>20.25088847520731</v>
       </c>
       <c r="D15">
         <v>2.481860660471465</v>
       </c>
       <c r="E15">
-        <v>25.09750698360829</v>
+        <v>12.61397775786644</v>
       </c>
       <c r="F15">
         <v>62.28851525852527</v>
       </c>
       <c r="G15">
-        <v>12.61397775786644</v>
+        <v>25.09750698360829</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>26.18333762939046</v>
+      </c>
+      <c r="C16">
         <v>26.94170476591011</v>
-      </c>
-      <c r="C16">
-        <v>26.18333762939046</v>
       </c>
       <c r="D16">
         <v>3.711717609144468</v>
       </c>
       <c r="E16">
-        <v>17.59457783290511</v>
+        <v>17.09931779923806</v>
       </c>
       <c r="F16">
         <v>65.30610436785683</v>
       </c>
       <c r="G16">
-        <v>17.09931779923806</v>
+        <v>17.59457783290511</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.62507940127368</v>
+      </c>
+      <c r="C17">
         <v>36.61905304819454</v>
-      </c>
-      <c r="C17">
-        <v>26.62507940127368</v>
       </c>
       <c r="D17">
         <v>2.730818840902015</v>
       </c>
       <c r="E17">
+        <v>16.30997635367715</v>
+      </c>
+      <c r="F17">
+        <v>61.25794446606204</v>
+      </c>
+      <c r="G17">
         <v>22.43207918026081</v>
-      </c>
-      <c r="F17">
-        <v>61.25794446606205</v>
-      </c>
-      <c r="G17">
-        <v>16.30997635367715</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>24.56194073015549</v>
+      </c>
+      <c r="C18">
         <v>37.28862576979348</v>
-      </c>
-      <c r="C18">
-        <v>24.56194073015549</v>
       </c>
       <c r="D18">
         <v>2.681782928053287</v>
       </c>
       <c r="E18">
-        <v>23.03892199833927</v>
+        <v>15.17569030576315</v>
       </c>
       <c r="F18">
         <v>61.78538769589758</v>
       </c>
       <c r="G18">
-        <v>15.17569030576315</v>
+        <v>23.03892199833927</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>21.69824263816307</v>
+      </c>
+      <c r="C19">
         <v>36.83350586826646</v>
-      </c>
-      <c r="C19">
-        <v>21.69824263816307</v>
       </c>
       <c r="D19">
         <v>2.714919409454152</v>
       </c>
       <c r="E19">
-        <v>23.23415102355514</v>
+        <v>13.68700140040596</v>
       </c>
       <c r="F19">
         <v>63.0788475760389</v>
       </c>
       <c r="G19">
-        <v>13.68700140040596</v>
+        <v>23.23415102355514</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>24.16428885881528</v>
+      </c>
+      <c r="C20">
         <v>35.88788703918084</v>
-      </c>
-      <c r="C20">
-        <v>24.16428885881528</v>
       </c>
       <c r="D20">
         <v>2.786455493766583</v>
       </c>
       <c r="E20">
-        <v>22.42261739824942</v>
+        <v>15.09775716777233</v>
       </c>
       <c r="F20">
         <v>62.47962543397826</v>
       </c>
       <c r="G20">
-        <v>15.09775716777233</v>
+        <v>22.42261739824942</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>18.6142933687138</v>
+      </c>
+      <c r="C21">
         <v>33.07478376240655</v>
-      </c>
-      <c r="C21">
-        <v>18.6142933687138</v>
       </c>
       <c r="D21">
         <v>3.023451361567538</v>
       </c>
       <c r="E21">
+        <v>12.27134723261818</v>
+      </c>
+      <c r="F21">
+        <v>65.92432486985189</v>
+      </c>
+      <c r="G21">
         <v>21.80432789752992</v>
-      </c>
-      <c r="F21">
-        <v>65.9243248698519</v>
-      </c>
-      <c r="G21">
-        <v>12.27134723261818</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>25.9632231337296</v>
+      </c>
+      <c r="C22">
         <v>44.25340996545005</v>
-      </c>
-      <c r="C22">
-        <v>25.9632231337296</v>
       </c>
       <c r="D22">
         <v>2.259712869089026</v>
       </c>
       <c r="E22">
-        <v>25.99828768770502</v>
+        <v>15.25304705010918</v>
       </c>
       <c r="F22">
         <v>58.74866526218579</v>
       </c>
       <c r="G22">
-        <v>15.25304705010918</v>
+        <v>25.99828768770502</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>24.37674747487853</v>
+      </c>
+      <c r="C23">
         <v>31.12078416617473</v>
-      </c>
-      <c r="C23">
-        <v>24.37674747487853</v>
       </c>
       <c r="D23">
         <v>3.213286640401893</v>
       </c>
       <c r="E23">
-        <v>20.01368371429406</v>
+        <v>15.67661378133591</v>
       </c>
       <c r="F23">
         <v>64.30970250437002</v>
       </c>
       <c r="G23">
-        <v>15.67661378133591</v>
+        <v>20.01368371429406</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>14.62804403424886</v>
+      </c>
+      <c r="C24">
         <v>33.18414322250639</v>
-      </c>
-      <c r="C24">
-        <v>14.62804403424886</v>
       </c>
       <c r="D24">
         <v>3.013487475915221</v>
       </c>
       <c r="E24">
+        <v>9.89637208252619</v>
+      </c>
+      <c r="F24">
+        <v>67.65342009742153</v>
+      </c>
+      <c r="G24">
         <v>22.45020782005228</v>
-      </c>
-      <c r="F24">
-        <v>67.65342009742152</v>
-      </c>
-      <c r="G24">
-        <v>9.896372082526188</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.24274500306299</v>
+      </c>
+      <c r="C25">
         <v>31.02659809382702</v>
-      </c>
-      <c r="C25">
-        <v>27.24274500306299</v>
       </c>
       <c r="D25">
         <v>3.22304107261749</v>
       </c>
       <c r="E25">
-        <v>19.60366896502061</v>
+        <v>17.21290078672116</v>
       </c>
       <c r="F25">
         <v>63.18343024825823</v>
       </c>
       <c r="G25">
-        <v>17.21290078672115</v>
+        <v>19.60366896502061</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>26.84533811153951</v>
+      </c>
+      <c r="C26">
         <v>21.92722531705583</v>
-      </c>
-      <c r="C26">
-        <v>26.84533811153951</v>
       </c>
       <c r="D26">
         <v>4.560540540540541</v>
       </c>
       <c r="E26">
-        <v>14.73875613333771</v>
+        <v>18.04454900343514</v>
       </c>
       <c r="F26">
         <v>67.21669486322716</v>
       </c>
       <c r="G26">
-        <v>18.04454900343514</v>
+        <v>14.73875613333771</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>24.24442531514216</v>
+      </c>
+      <c r="C27">
         <v>31.75241441930121</v>
-      </c>
-      <c r="C27">
-        <v>24.24442531514216</v>
       </c>
       <c r="D27">
         <v>3.149366806551046</v>
       </c>
       <c r="E27">
-        <v>20.35452415148537</v>
+        <v>15.54161312268501</v>
       </c>
       <c r="F27">
         <v>64.10386272582961</v>
       </c>
       <c r="G27">
-        <v>15.54161312268501</v>
+        <v>20.35452415148537</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>24.73511451095546</v>
+      </c>
+      <c r="C28">
         <v>32.63258301927375</v>
-      </c>
-      <c r="C28">
-        <v>24.73511451095546</v>
       </c>
       <c r="D28">
         <v>3.06442183693939</v>
       </c>
       <c r="E28">
-        <v>20.73651933110686</v>
+        <v>15.7180380085335</v>
       </c>
       <c r="F28">
         <v>63.54544266035964</v>
       </c>
       <c r="G28">
-        <v>15.7180380085335</v>
+        <v>20.73651933110686</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.7999741791109</v>
+      </c>
+      <c r="C29">
         <v>30.19537806085123</v>
-      </c>
-      <c r="C29">
-        <v>28.7999741791109</v>
       </c>
       <c r="D29">
         <v>3.311765125062353</v>
       </c>
       <c r="E29">
-        <v>18.99135895197688</v>
+        <v>18.11372079332535</v>
       </c>
       <c r="F29">
         <v>62.89492025469777</v>
       </c>
       <c r="G29">
-        <v>18.11372079332535</v>
+        <v>18.99135895197688</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>24.45419637959408</v>
+      </c>
+      <c r="C30">
         <v>38.27913172948828</v>
-      </c>
-      <c r="C30">
-        <v>24.45419637959408</v>
       </c>
       <c r="D30">
         <v>2.612389452997052</v>
       </c>
       <c r="E30">
-        <v>23.5226134525002</v>
+        <v>15.02715925726173</v>
       </c>
       <c r="F30">
-        <v>61.45022729023808</v>
+        <v>61.45022729023807</v>
       </c>
       <c r="G30">
-        <v>15.02715925726173</v>
+        <v>23.52261345250019</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.01502586419246</v>
+      </c>
+      <c r="C31">
         <v>27.57512932096231</v>
-      </c>
-      <c r="C31">
-        <v>23.01502586419246</v>
       </c>
       <c r="D31">
         <v>3.626456247441099</v>
       </c>
       <c r="E31">
-        <v>18.31137585790912</v>
+        <v>15.28322076293424</v>
       </c>
       <c r="F31">
         <v>66.40540337915664</v>
       </c>
       <c r="G31">
-        <v>15.28322076293424</v>
+        <v>18.31137585790912</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>25.27669025749134</v>
+      </c>
+      <c r="C32">
         <v>36.59275711489234</v>
-      </c>
-      <c r="C32">
-        <v>25.27669025749134</v>
       </c>
       <c r="D32">
         <v>2.732781235533152</v>
       </c>
       <c r="E32">
-        <v>22.6063396823182</v>
+        <v>15.61547942975418</v>
       </c>
       <c r="F32">
         <v>61.77818088792763</v>
       </c>
       <c r="G32">
-        <v>15.61547942975418</v>
+        <v>22.6063396823182</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>23.40445407667588</v>
+      </c>
+      <c r="C33">
         <v>41.58134668559899</v>
-      </c>
-      <c r="C33">
-        <v>23.40445407667588</v>
       </c>
       <c r="D33">
         <v>2.404924514737599</v>
       </c>
       <c r="E33">
-        <v>25.20298504082349</v>
+        <v>14.18573838993511</v>
       </c>
       <c r="F33">
         <v>60.6112765692414</v>
       </c>
       <c r="G33">
-        <v>14.18573838993511</v>
+        <v>25.20298504082349</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>26.90396574892965</v>
+      </c>
+      <c r="C34">
         <v>31.00210517942322</v>
-      </c>
-      <c r="C34">
-        <v>26.90396574892965</v>
       </c>
       <c r="D34">
         <v>3.22558740515377</v>
       </c>
       <c r="E34">
-        <v>19.63325728843566</v>
+        <v>17.03795527984282</v>
       </c>
       <c r="F34">
         <v>63.32878743172152</v>
       </c>
       <c r="G34">
-        <v>17.03795527984282</v>
+        <v>19.63325728843566</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>21.82837325590774</v>
+      </c>
+      <c r="C35">
         <v>30.6073070408904</v>
-      </c>
-      <c r="C35">
-        <v>21.82837325590774</v>
       </c>
       <c r="D35">
         <v>3.267193675889328</v>
       </c>
       <c r="E35">
-        <v>20.07883389328325</v>
+        <v>14.31972699134944</v>
       </c>
       <c r="F35">
         <v>65.60143911536731</v>
       </c>
       <c r="G35">
-        <v>14.31972699134944</v>
+        <v>20.07883389328325</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>23.99802890932983</v>
+      </c>
+      <c r="C36">
         <v>37.37680683311432</v>
-      </c>
-      <c r="C36">
-        <v>23.99802890932983</v>
       </c>
       <c r="D36">
         <v>2.675455943748627</v>
       </c>
       <c r="E36">
-        <v>23.16148404498957</v>
+        <v>14.87098580080411</v>
       </c>
       <c r="F36">
         <v>61.96753015420632</v>
       </c>
       <c r="G36">
-        <v>14.87098580080411</v>
+        <v>23.16148404498957</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>33.30439233032956</v>
+      </c>
+      <c r="C37">
         <v>19.5744758632035</v>
-      </c>
-      <c r="C37">
-        <v>33.30439233032956</v>
       </c>
       <c r="D37">
         <v>5.108693622186945</v>
       </c>
       <c r="E37">
-        <v>12.80391207398507</v>
+        <v>21.784823974605</v>
       </c>
       <c r="F37">
         <v>65.41126395140994</v>
       </c>
       <c r="G37">
-        <v>21.784823974605</v>
+        <v>12.80391207398507</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>34.56161123270305</v>
+      </c>
+      <c r="C38">
         <v>17.99600540585794</v>
-      </c>
-      <c r="C38">
-        <v>34.56161123270305</v>
       </c>
       <c r="D38">
         <v>5.556788728650229</v>
       </c>
       <c r="E38">
-        <v>11.79620251179855</v>
+        <v>22.65479232976371</v>
       </c>
       <c r="F38">
         <v>65.54900515843772</v>
       </c>
       <c r="G38">
-        <v>22.65479232976371</v>
+        <v>11.79620251179855</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>32.99050632911392</v>
+      </c>
+      <c r="C39">
         <v>19.09810126582278</v>
-      </c>
-      <c r="C39">
-        <v>32.99050632911392</v>
       </c>
       <c r="D39">
         <v>5.236122618061309</v>
       </c>
       <c r="E39">
-        <v>12.55722014148981</v>
+        <v>21.6916354556804</v>
       </c>
       <c r="F39">
         <v>65.75114440282981</v>
       </c>
       <c r="G39">
-        <v>21.6916354556804</v>
+        <v>12.55722014148981</v>
       </c>
     </row>
     <row r="40">
@@ -1348,22 +1348,22 @@
         </is>
       </c>
       <c r="B40">
+        <v>29.25192145226762</v>
+      </c>
+      <c r="C40">
         <v>28.21753106261977</v>
-      </c>
-      <c r="C40">
-        <v>29.25192145226762</v>
       </c>
       <c r="D40">
         <v>3.543896160797415</v>
       </c>
       <c r="E40">
-        <v>17.91936824061291</v>
+        <v>18.57625144756384</v>
       </c>
       <c r="F40">
         <v>63.50438031182324</v>
       </c>
       <c r="G40">
-        <v>18.57625144756384</v>
+        <v>17.91936824061291</v>
       </c>
     </row>
     <row r="41">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B41">
+        <v>30.98347513512116</v>
+      </c>
+      <c r="C41">
         <v>25.24502831725672</v>
-      </c>
-      <c r="C41">
-        <v>30.98347513512116</v>
       </c>
       <c r="D41">
         <v>3.961175988526941</v>
       </c>
       <c r="E41">
-        <v>16.15904125008277</v>
+        <v>19.83215255247302</v>
       </c>
       <c r="F41">
         <v>64.00880619744422</v>
       </c>
       <c r="G41">
-        <v>19.83215255247302</v>
+        <v>16.15904125008277</v>
       </c>
     </row>
     <row r="42">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B42">
+        <v>20.04826754007929</v>
+      </c>
+      <c r="C42">
         <v>29.92156524737114</v>
-      </c>
-      <c r="C42">
-        <v>20.04826754007929</v>
       </c>
       <c r="D42">
         <v>3.342071150799366</v>
       </c>
       <c r="E42">
+        <v>13.36820023563895</v>
+      </c>
+      <c r="F42">
+        <v>66.68007701370729</v>
+      </c>
+      <c r="G42">
         <v>19.95172275065375</v>
-      </c>
-      <c r="F42">
-        <v>66.68007701370728</v>
-      </c>
-      <c r="G42">
-        <v>13.36820023563895</v>
       </c>
     </row>
     <row r="43">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B43">
+        <v>29.38023963557019</v>
+      </c>
+      <c r="C43">
         <v>30.18221490640432</v>
-      </c>
-      <c r="C43">
-        <v>29.38023963557019</v>
       </c>
       <c r="D43">
         <v>3.313209461601877</v>
       </c>
       <c r="E43">
-        <v>18.91561206741439</v>
+        <v>18.41300305883764</v>
       </c>
       <c r="F43">
         <v>62.67138487374798</v>
       </c>
       <c r="G43">
-        <v>18.41300305883764</v>
+        <v>18.91561206741439</v>
       </c>
     </row>
     <row r="44">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B44">
+        <v>29.71694394070803</v>
+      </c>
+      <c r="C44">
         <v>33.2030502021829</v>
-      </c>
-      <c r="C44">
-        <v>29.71694394070803</v>
       </c>
       <c r="D44">
         <v>3.011771490603162</v>
       </c>
       <c r="E44">
-        <v>20.37997262205998</v>
+        <v>18.2402068555468</v>
       </c>
       <c r="F44">
         <v>61.37982052239322</v>
       </c>
       <c r="G44">
-        <v>18.2402068555468</v>
+        <v>20.37997262205998</v>
       </c>
     </row>
     <row r="45">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B45">
+        <v>33.62782992821646</v>
+      </c>
+      <c r="C45">
         <v>32.13694091662065</v>
-      </c>
-      <c r="C45">
-        <v>33.62782992821646</v>
       </c>
       <c r="D45">
         <v>3.111683848797251</v>
       </c>
       <c r="E45">
+        <v>20.28647568287808</v>
+      </c>
+      <c r="F45">
+        <v>60.32644903397735</v>
+      </c>
+      <c r="G45">
         <v>19.38707528314457</v>
-      </c>
-      <c r="F45">
-        <v>60.32644903397734</v>
-      </c>
-      <c r="G45">
-        <v>20.28647568287808</v>
       </c>
     </row>
     <row r="46">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B46">
+        <v>29.19514212336221</v>
+      </c>
+      <c r="C46">
         <v>36.24689853306055</v>
-      </c>
-      <c r="C46">
-        <v>29.19514212336221</v>
       </c>
       <c r="D46">
         <v>2.758856731115648</v>
       </c>
       <c r="E46">
-        <v>21.9091220038414</v>
+        <v>17.64674928302681</v>
       </c>
       <c r="F46">
         <v>60.44412871313179</v>
       </c>
       <c r="G46">
-        <v>17.64674928302681</v>
+        <v>21.9091220038414</v>
       </c>
     </row>
     <row r="47">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B47">
+        <v>29.41825476429288</v>
+      </c>
+      <c r="C47">
         <v>37.49247743229689</v>
-      </c>
-      <c r="C47">
-        <v>29.41825476429288</v>
       </c>
       <c r="D47">
         <v>2.667201712145532</v>
       </c>
       <c r="E47">
-        <v>22.46259239228412</v>
+        <v>17.62514271978848</v>
       </c>
       <c r="F47">
         <v>59.91226488792741</v>
       </c>
       <c r="G47">
-        <v>17.62514271978848</v>
+        <v>22.46259239228412</v>
       </c>
     </row>
     <row r="48">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B48">
+        <v>32.56806475349522</v>
+      </c>
+      <c r="C48">
         <v>40.88300220750552</v>
-      </c>
-      <c r="C48">
-        <v>32.56806475349522</v>
       </c>
       <c r="D48">
         <v>2.446004319654428</v>
       </c>
       <c r="E48">
-        <v>23.5703376887833</v>
+        <v>18.77651450873919</v>
       </c>
       <c r="F48">
         <v>57.65314780247752</v>
       </c>
       <c r="G48">
-        <v>18.77651450873919</v>
+        <v>23.5703376887833</v>
       </c>
     </row>
     <row r="49">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B49">
+        <v>27.57845749970168</v>
+      </c>
+      <c r="C49">
         <v>31.83445368123782</v>
-      </c>
-      <c r="C49">
-        <v>27.57845749970168</v>
       </c>
       <c r="D49">
         <v>3.141250702817517</v>
       </c>
       <c r="E49">
-        <v>19.96980887269824</v>
+        <v>17.30001497080693</v>
       </c>
       <c r="F49">
         <v>62.73017615649484</v>
       </c>
       <c r="G49">
-        <v>17.30001497080693</v>
+        <v>19.96980887269824</v>
       </c>
     </row>
     <row r="50">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B50">
+        <v>29.16650136866744</v>
+      </c>
+      <c r="C50">
         <v>31.19371603126116</v>
-      </c>
-      <c r="C50">
-        <v>29.16650136866744</v>
       </c>
       <c r="D50">
         <v>3.205773877654839</v>
       </c>
       <c r="E50">
+        <v>18.18811538271238</v>
+      </c>
+      <c r="F50">
+        <v>62.35960615506406</v>
+      </c>
+      <c r="G50">
         <v>19.45227846222354</v>
-      </c>
-      <c r="F50">
-        <v>62.35960615506408</v>
-      </c>
-      <c r="G50">
-        <v>18.18811538271239</v>
       </c>
     </row>
     <row r="51">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="B51">
+        <v>27.32310476118672</v>
+      </c>
+      <c r="C51">
         <v>30.61786104723489</v>
-      </c>
-      <c r="C51">
-        <v>27.32310476118672</v>
       </c>
       <c r="D51">
         <v>3.26606747106624</v>
       </c>
       <c r="E51">
+        <v>17.29956798816145</v>
+      </c>
+      <c r="F51">
+        <v>63.31479580876913</v>
+      </c>
+      <c r="G51">
         <v>19.38563620306943</v>
-      </c>
-      <c r="F51">
-        <v>63.31479580876912</v>
-      </c>
-      <c r="G51">
-        <v>17.29956798816144</v>
       </c>
     </row>
     <row r="52">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="B52">
+        <v>29.97454352324964</v>
+      </c>
+      <c r="C52">
         <v>24.0206582055931</v>
-      </c>
-      <c r="C52">
-        <v>29.97454352324964</v>
       </c>
       <c r="D52">
         <v>4.163083257090577</v>
       </c>
       <c r="E52">
+        <v>19.46459577099636</v>
+      </c>
+      <c r="F52">
+        <v>64.93708821920416</v>
+      </c>
+      <c r="G52">
         <v>15.59831600979949</v>
-      </c>
-      <c r="F52">
-        <v>64.93708821920414</v>
-      </c>
-      <c r="G52">
-        <v>19.46459577099636</v>
       </c>
     </row>
     <row r="53">
@@ -1673,22 +1673,22 @@
         </is>
       </c>
       <c r="B53">
+        <v>27.08237308224139</v>
+      </c>
+      <c r="C53">
         <v>30.50470797392506</v>
-      </c>
-      <c r="C53">
-        <v>27.08237308224139</v>
       </c>
       <c r="D53">
         <v>3.278182504991636</v>
       </c>
       <c r="E53">
-        <v>19.35736595251277</v>
+        <v>17.18565563923912</v>
       </c>
       <c r="F53">
         <v>63.45697840824811</v>
       </c>
       <c r="G53">
-        <v>17.18565563923912</v>
+        <v>19.35736595251277</v>
       </c>
     </row>
   </sheetData>
